--- a/out/global_metric/excel/googlenet.xlsx
+++ b/out/global_metric/excel/googlenet.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -465,20 +485,32 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8928571343421936</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7775510111141889</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>0.8897959132865056</v>
+      </c>
+      <c r="D2" t="n">
+        <v>61</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>89</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>googlenet</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -489,20 +521,32 @@
         <v>28</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7388888803492065</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>0.8530612194135778</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>86</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>googlenet</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -513,20 +557,32 @@
         <v>47</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9107142857142856</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7209750484830068</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>0.900694541962565</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>93</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>googlenet</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -537,20 +593,32 @@
         <v>66</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.886904776096344</v>
       </c>
       <c r="C5" t="n">
-        <v>0.685034006148121</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>0.8829182357468124</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>90</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>googlenet</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -561,140 +629,32 @@
         <v>85</v>
       </c>
       <c r="B6" t="n">
-        <v>0.886904761904762</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7714285620211641</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>0.9011764654900072</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>92</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>googlenet</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>104</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6761904684166666</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>googlenet</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>123</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8214285714285716</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7045351394964637</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>googlenet</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>142</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8809523809523812</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7426303770123367</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>googlenet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>161</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.8630952380952381</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.748412689774471</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>googlenet</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>180</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8749999999999998</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7222222140410056</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>googlenet</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>nan</t>
         </is>

--- a/out/global_metric/excel/googlenet.xlsx
+++ b/out/global_metric/excel/googlenet.xlsx
@@ -495,28 +495,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8928571343421936</v>
+        <v>0.6689304113388062</v>
       </c>
       <c r="C2" t="n">
-        <v>0.887700529652494</v>
+        <v>0.6639082051680767</v>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>233</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9689002403846154</v>
+        <v>0.7270033437103656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.980691890601824</v>
+        <v>0.687631333807043</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -537,28 +537,28 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8214285969734192</v>
+        <v>0.6926994919776917</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8205128155557821</v>
+        <v>0.6914150530176755</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9732572115384616</v>
+        <v>0.7758849302432838</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9834126363550511</v>
+        <v>0.7662078597010518</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -579,28 +579,28 @@
         <v>55</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8809523582458496</v>
+        <v>0.7130730152130127</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8758681787324347</v>
+        <v>0.7125128110558924</v>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>223</v>
       </c>
       <c r="H4" t="n">
-        <v>0.962439903846154</v>
+        <v>0.7952150351666092</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9794874758418536</v>
+        <v>0.7872081665358721</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -621,28 +621,28 @@
         <v>78</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8809523582458496</v>
+        <v>0.7011884450912476</v>
       </c>
       <c r="C5" t="n">
-        <v>0.877551015328863</v>
+        <v>0.6962636488961447</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>244</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9517728365384616</v>
+        <v>0.7793612360198318</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9596110874187972</v>
+        <v>0.7523281899614164</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -663,28 +663,28 @@
         <v>101</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8452380895614624</v>
+        <v>0.7130730152130127</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8425378464367224</v>
+        <v>0.7129538529330478</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9640925480769232</v>
+        <v>0.7834428686728929</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9738618387774972</v>
+        <v>0.7726934075612614</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>

--- a/out/global_metric/excel/googlenet.xlsx
+++ b/out/global_metric/excel/googlenet.xlsx
@@ -495,28 +495,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6689304113388062</v>
+        <v>0.6943972706794739</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6639082051680767</v>
+        <v>0.6940789423495237</v>
       </c>
       <c r="D2" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7270033437103656</v>
+        <v>0.7548368499942351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.687631333807043</v>
+        <v>0.7229442935091113</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -537,28 +537,28 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6926994919776917</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6914150530176755</v>
+        <v>0.7079114238783353</v>
       </c>
       <c r="D3" t="n">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7758849302432838</v>
+        <v>0.7920154502478958</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7662078597010518</v>
+        <v>0.793826346506092</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -579,28 +579,28 @@
         <v>55</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7130730152130127</v>
+        <v>0.7368420958518982</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7125128110558924</v>
+        <v>0.7344415791526475</v>
       </c>
       <c r="D4" t="n">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7952150351666092</v>
+        <v>0.8155309581459704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7872081665358721</v>
+        <v>0.7930808750704806</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -621,28 +621,28 @@
         <v>78</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7011884450912476</v>
+        <v>0.7215619683265686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6962636488961447</v>
+        <v>0.7204588550212339</v>
       </c>
       <c r="D5" t="n">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="E5" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>244</v>
+        <v>194</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7793612360198318</v>
+        <v>0.7845151619970022</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7523281899614164</v>
+        <v>0.770679665248462</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -663,28 +663,28 @@
         <v>101</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7130730152130127</v>
+        <v>0.7334465384483337</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7129538529330478</v>
+        <v>0.7333358275154447</v>
       </c>
       <c r="D6" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G6" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7834428686728929</v>
+        <v>0.8153695376455667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7726934075612614</v>
+        <v>0.810177282414103</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
